--- a/backend/src/main/resources/plan-curricular-plantilla-etapa2.xlsx
+++ b/backend/src/main/resources/plan-curricular-plantilla-etapa2.xlsx
@@ -677,6 +677,436 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>54720</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>29880</colOff>
+      <row>3</row>
+      <rowOff>160560</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1323360" y="0"/>
+          <a:ext cx="659880" cy="791640"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>24</col>
+      <colOff>479439</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 4"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5417" t="3475" r="-1514" b="90112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>54720</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>29880</colOff>
+      <row>3</row>
+      <rowOff>160560</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1323360" y="0"/>
+          <a:ext cx="659880" cy="791640"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>24</col>
+      <colOff>479439</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 4"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5417" t="3475" r="-1514" b="90112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>54720</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>29880</colOff>
+      <row>3</row>
+      <rowOff>160560</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1323360" y="0"/>
+          <a:ext cx="659880" cy="791640"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>24</col>
+      <colOff>479439</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 4"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5417" t="3475" r="-1514" b="90112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>54720</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>29880</colOff>
+      <row>3</row>
+      <rowOff>160560</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1323360" y="0"/>
+          <a:ext cx="659880" cy="791640"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>24</col>
+      <colOff>479439</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 4"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5417" t="3475" r="-1514" b="90112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>54720</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>29880</colOff>
+      <row>3</row>
+      <rowOff>160560</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1323360" y="0"/>
+          <a:ext cx="659880" cy="791640"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>24</col>
+      <colOff>479439</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 4"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5417" t="3475" r="-1514" b="90112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -893,14 +1323,14 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="59" t="inlineStr">
         <is>
-          <t>2. Por cada mes, cargá hasta 4 bloques temáticos con: Capacidades, Temas/Contenidos, Actividades, Instrumentos de evaluación e Indicadores (Conceptual, Procedimental, Actitudinal).</t>
+          <t>2. Por cada mes, completá los bloques temáticos con: Capacidades, Temas/Contenidos, Actividades, Instrumentos de evaluación e Indicadores (Conceptual, Procedimental, Actitudinal).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="59" t="inlineStr">
         <is>
-          <t>3. La hoja "Marzo" ya trae el primer bloque como ejemplo de referencia — no lo dejes así, reemplazalo por tu propio contenido.</t>
+          <t>3. La cantidad de meses y de bloques por mes ya viene armada según la configuración elegida al descargar la plantilla.</t>
         </is>
       </c>
     </row>
@@ -2052,6 +2482,7 @@
   </mergeCells>
   <pageMargins left="1.29930555555556" right="0.905555555555556" top="0.551388888888889" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3184,6 +3615,7 @@
   </mergeCells>
   <pageMargins left="1.29930555555556" right="0.905555555555556" top="0.551388888888889" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4316,6 +4748,7 @@
   </mergeCells>
   <pageMargins left="1.29930555555556" right="0.905555555555556" top="0.551388888888889" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5448,6 +5881,7 @@
   </mergeCells>
   <pageMargins left="1.29930555555556" right="0.905555555555556" top="0.551388888888889" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6580,5 +7014,6 @@
   </mergeCells>
   <pageMargins left="1.29930555555556" right="0.905555555555556" top="0.551388888888889" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>